--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-130033</t>
+          <t>I-130242</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.150369</t>
+          <t>-13.1568293</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-74.227737</t>
+          <t>-74.2313391</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>JR. LIBERTAD CON PJE. LOS ANGELES</t>
+          <t>Avenida Perú / Jirón Venezuela</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-130218</t>
+          <t>I-130466</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-13.156652</t>
+          <t>-13.1477877</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-74.2321888</t>
+          <t>-74.223604</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Perú / Jr. Humanga</t>
+          <t>Avenida Independencia / Jirón Las Magnolias</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-130242</t>
+          <t>I-131657</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050104</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CARMEN ALTO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.1568293</t>
+          <t>-13.1811054</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.2313391</t>
+          <t>-74.2267442</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Perú / Jr. Venezuela</t>
+          <t>Jirón Cangallo / Jirón Del Porvenir / Prolongación Jirón Porvenir</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-130313</t>
+          <t>I-131869</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050104</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,27 +659,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CARMEN ALTO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.1497508</t>
+          <t>-13.1880799</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.2279513</t>
+          <t>-74.2219295</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Agustin Gamarra / Pasaje Los Laureles</t>
+          <t>Avenida Abrahan Valdelomar / Avenida Gran Mariscal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-130315</t>
+          <t>I-136120</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050104</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,27 +711,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CARMEN ALTO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-13.1497045</t>
+          <t>-13.1823986</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.2278748</t>
+          <t>-74.2215016</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jr. Libertad / Pasaje Los Laureles</t>
+          <t>Avenida Los Libertadores / Jirón Atahualpa</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-130464</t>
+          <t>I-131686</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050104</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -763,27 +763,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CARMEN ALTO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-13.1502741</t>
+          <t>-13.1772559</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.2250455</t>
+          <t>-74.2229851</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jr. Las Magnolias / Jr. Las Palmeras / Jr. Los Jasmines</t>
+          <t>Jirón Huancavelica / Jirón Progreso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-130466</t>
+          <t>I-131685</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050104</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CARMEN ALTO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.1477877</t>
+          <t>-13.177515</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.223604</t>
+          <t>-74.2240321</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Jr. Las Magnolias</t>
+          <t>Jirón Huancavelica / Jirón Miguel Grau</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-130467</t>
+          <t>I-130046</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.1477427</t>
+          <t>-13.1576088</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.2235325</t>
+          <t>-74.2245429</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Jr. Las Magnolias</t>
+          <t>Avenida Mariscal Cáceres / Jirón Asamblea</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-130493</t>
+          <t>I-130089</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -924,22 +924,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-13.1507491</t>
+          <t>-13.1622879</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-74.2228979</t>
+          <t>-74.2374572</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Jr. Bolivar / Jr. Las Palmeras</t>
+          <t>Avenida Jose Carlos Mareategui / Avenida Los Andes / Jirón Nueva Democracia / Prolongación Los Andes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-130494</t>
+          <t>I-130182</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -976,22 +976,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-13.1507257</t>
+          <t>-13.1647184</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-74.2229646</t>
+          <t>-74.2354889</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Jr. Las Palmeras</t>
+          <t>Avenida Jose Carlos Mareategui / Jirón Ica</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-130642</t>
+          <t>I-281516</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-13.1608935</t>
+          <t>-13.1444425</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-74.219722</t>
+          <t>-74.2259067</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jr. Puno / Prolongación Jr. Cusco / Prolongación Jr. Puno</t>
+          <t>Avenida Independencia / Jirón Los Alamos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-133221</t>
+          <t>I-281523</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-13.1306062</t>
+          <t>-13.1554223</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-74.2335154</t>
+          <t>-74.233729</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jr. Quriwillka</t>
+          <t>Jirón Juan Domingo Nieto / Jirón Pokra</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-133281</t>
+          <t>I-283895</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1127,27 +1127,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.1503379</t>
+          <t>-13.1379229</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-74.2277327</t>
+          <t>-74.1895613</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jr. Libertad / Pasaje Las Cucardas</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-133282</t>
+          <t>I-283898</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1179,27 +1179,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-13.1503717</t>
+          <t>-13.1529013</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-74.2277256</t>
+          <t>-74.1948981</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Nery Garcia Zarate / Jr. Libertad</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-281464</t>
+          <t>I-283899</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1231,27 +1231,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-13.1503873</t>
+          <t>-13.1476355</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-74.2277223</t>
+          <t>-74.1929479</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Jr. Libertad</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-281519</t>
+          <t>I-283900</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1283,27 +1283,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-13.1511841</t>
+          <t>-13.1468196</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-74.2230705</t>
+          <t>-74.1920251</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Independencia</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1315,7 +1315,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>l-281533</t>
+          <t>I-375617</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1340,285 +1340,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-13.1477704</t>
+          <t>-13.1503668</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-74.2235152</t>
+          <t>-74.2228802</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Independencia</t>
+          <t>Avenida Independencia / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>l-285896</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-13.1509099</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-74.2230088</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Avenida Independencia</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>l-321798</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-13.130698</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-74.2333682</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Jr. 5 de Marzo</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>l-375617</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-13.1503668</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-74.2228802</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Avenida Independencia</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>l-383919</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-13.1508873</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-74.2229382</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Avenida Independencia</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>l-756526</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-13.0902934</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-74.2338524</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
         <is>
           <t>050101</t>
         </is>

--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1364,6 +1364,162 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-283903</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>050116</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-13.1418276</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-74.190996</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-283904</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>050116</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-13.1448897</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-74.1923288</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-283906</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>050116</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-13.1489812</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-74.1935572</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,12 +587,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I-131657</t>
+          <t>I-130046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>050104</t>
+          <t>050101</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.1811054</t>
+          <t>-13.1576088</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.2267442</t>
+          <t>-74.2245429</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jirón Cangallo / Jirón Del Porvenir / Prolongación Jirón Porvenir</t>
+          <t>Avenida Mariscal Cáceres / Jirón Asamblea</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I-131869</t>
+          <t>I-130089</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>050104</t>
+          <t>050101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.1880799</t>
+          <t>-13.1622879</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.2219295</t>
+          <t>-74.2374572</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Abrahan Valdelomar / Avenida Gran Mariscal</t>
+          <t>Avenida Jose Carlos Mareategui / Avenida Los Andes / Jirón Nueva Democracia / Prolongación Los Andes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I-136120</t>
+          <t>I-130182</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>050104</t>
+          <t>050101</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,22 +711,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-13.1823986</t>
+          <t>-13.1647184</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.2215016</t>
+          <t>-74.2354889</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Los Libertadores / Jirón Atahualpa</t>
+          <t>Avenida Jose Carlos Mareategui / Jirón Ica</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I-131686</t>
+          <t>I-281516</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>050104</t>
+          <t>050101</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-13.1772559</t>
+          <t>-13.1444425</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.2229851</t>
+          <t>-74.2259067</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jirón Huancavelica / Jirón Progreso</t>
+          <t>11 de Junio / Avenida Independencia / Jirón Los Alamos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I-131685</t>
+          <t>I-281523</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>050104</t>
+          <t>050101</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CARMEN ALTO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.177515</t>
+          <t>-13.1554223</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.2240321</t>
+          <t>-74.233729</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jirón Huancavelica / Jirón Miguel Grau</t>
+          <t>Jirón Juan Domingo Nieto / Jirón Pokra</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I-130046</t>
+          <t>I-283895</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,22 +867,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.1576088</t>
+          <t>-13.1379229</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.2245429</t>
+          <t>-74.1895613</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Cáceres / Jirón Asamblea</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I-130089</t>
+          <t>I-283898</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,22 +919,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-13.1622879</t>
+          <t>-13.1529013</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-74.2374572</t>
+          <t>-74.1948981</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Jose Carlos Mareategui / Avenida Los Andes / Jirón Nueva Democracia / Prolongación Los Andes</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -951,12 +951,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I-130182</t>
+          <t>I-283899</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-13.1647184</t>
+          <t>-13.1476355</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-74.2354889</t>
+          <t>-74.1929479</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Jose Carlos Mareategui / Jirón Ica</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I-281516</t>
+          <t>I-283900</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>050116</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,22 +1023,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-13.1444425</t>
+          <t>-13.1468196</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-74.2259067</t>
+          <t>-74.1920251</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Jirón Los Alamos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I-281523</t>
+          <t>I-375617</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-13.1554223</t>
+          <t>-13.1503668</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-74.233729</t>
+          <t>-74.2228802</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jirón Juan Domingo Nieto / Jirón Pokra</t>
+          <t>Avenida Independencia / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I-283895</t>
+          <t>I-283903</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.1379229</t>
+          <t>-13.1418276</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-74.1895613</t>
+          <t>-74.190996</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I-283898</t>
+          <t>I-283904</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-13.1529013</t>
+          <t>-13.1448897</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-74.1948981</t>
+          <t>-74.1923288</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I-283899</t>
+          <t>I-283906</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-13.1476355</t>
+          <t>-13.1489812</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-74.1929479</t>
+          <t>-74.1935572</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I-283900</t>
+          <t>I-283910</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-13.1468196</t>
+          <t>-13.1540357</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-74.1920251</t>
+          <t>-74.1950155</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1307,214 +1307,6 @@
         </is>
       </c>
       <c r="J17" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>I-375617</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-13.1503668</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-74.2228802</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Avenida Independencia / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>I-283903</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-13.1418276</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-74.190996</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Calle s / n / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>I-283904</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-13.1448897</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-74.1923288</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Calle s / n / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>I-283906</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-13.1489812</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-74.1935572</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Calle s / n / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>050101</t>
         </is>

--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-130242</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-13.1568293</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-130466</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-13.1477877</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-130046</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-13.1576088</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-130089</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-13.1622879</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-130182</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-13.1647184</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-281516</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-13.1444425</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-281523</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-13.1554223</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-283895</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-13.1379229</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-283898</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-13.1529013</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-283899</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-13.1476355</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-283900</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-13.1468196</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-375617</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>050101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-13.1503668</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-283903</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-13.1418276</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-283904</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-13.1448897</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-283906</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-13.1489812</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-283910</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>050116</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ANDRES AVELINO CACERES DORREGARAY</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-13.1540357</t>
@@ -1304,11 +1224,6 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>050101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.2354889</t>
+          <t>-74.23548890000001</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
+++ b/Intersecciones/excels/AYACUCHO-HUAMANGA-AYACUCHO.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-130242</t>
+          <t>I-375617</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.1568293</t>
+          <t>-13.1503668</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-74.2313391</t>
+          <t>-74.2228802</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Perú / Jirón Venezuela</t>
+          <t>Avenida Independencia / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-130466</t>
+          <t>I-283910</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-13.1477877</t>
+          <t>-13.1540357</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-74.223604</t>
+          <t>-74.1950155</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Jirón Las Magnolias</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-130046</t>
+          <t>I-283906</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.1576088</t>
+          <t>-13.1489812</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.2245429</t>
+          <t>-74.1935572</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Cáceres / Jirón Asamblea</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-130089</t>
+          <t>I-283904</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.1622879</t>
+          <t>-13.1448897</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.2374572</t>
+          <t>-74.1923288</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Jose Carlos Mareategui / Avenida Los Andes / Jirón Nueva Democracia / Prolongación Los Andes</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-130182</t>
+          <t>I-283903</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-13.1647184</t>
+          <t>-13.1418276</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.23548890000001</t>
+          <t>-74.190996</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Jose Carlos Mareategui / Jirón Ica</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-281516</t>
+          <t>I-283900</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-13.1444425</t>
+          <t>-13.1468196</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.2259067</t>
+          <t>-74.1920251</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11 de Junio / Avenida Independencia / Jirón Los Alamos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-281523</t>
+          <t>I-283899</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.1554223</t>
+          <t>-13.1476355</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.233729</t>
+          <t>-74.1929479</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jirón Juan Domingo Nieto / Jirón Pokra</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-283895</t>
+          <t>I-283898</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.1379229</t>
+          <t>-13.1529013</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.1895613</t>
+          <t>-74.1948981</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-283898</t>
+          <t>I-283895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-13.1529013</t>
+          <t>-13.1379229</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-74.1948981</t>
+          <t>-74.1895613</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-283899</t>
+          <t>I-281523</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-13.1476355</t>
+          <t>-13.1554223</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-74.1929479</t>
+          <t>-74.233729</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Juan Domingo Nieto / Jirón Pokra</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-283900</t>
+          <t>I-281516</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-13.1468196</t>
+          <t>-13.1444425</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-74.1920251</t>
+          <t>-74.2259067</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Independencia / Jirón Los Alamos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-375617</t>
+          <t>I-130466</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-13.1503668</t>
+          <t>-13.1477877</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-74.2228802</t>
+          <t>-74.223604</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Independencia / Calle s / n</t>
+          <t>Avenida Independencia / Jirón Las Magnolias</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-283903</t>
+          <t>I-130242</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.1418276</t>
+          <t>-13.1568293</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-74.190996</t>
+          <t>-74.2313391</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Perú / Jirón Venezuela</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-283904</t>
+          <t>I-130182</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-13.1448897</t>
+          <t>-13.1647184</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-74.1923288</t>
+          <t>-74.2354889</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Jose Carlos Mareategui / Jirón Ica</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-283906</t>
+          <t>I-130089</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-13.1489812</t>
+          <t>-13.1622879</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-74.1935572</t>
+          <t>-74.2374572</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Jose Carlos Mareategui / Avenida Los Andes / Jirón Nueva Democracia / Prolongación Los Andes</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-283910</t>
+          <t>I-130046</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-13.1540357</t>
+          <t>-13.1576088</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-74.1950155</t>
+          <t>-74.2245429</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Mariscal Cáceres / Jirón Asamblea</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
